--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מתנאל סבח - שריטות ופחדים קאבר</v>
+        <v>ספיר יהודה לוי - מי המציא את המילה קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410322&amp;sid=43fe725fde6d02927362e89be5d6c20b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410326&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מתנאל סבח - שריטות ופחדים קאבר</v>
+        <v>ספיר יהודה לוי - מי המציא את המילה קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ליאור כהן - חוזה לך ברח קאבר</v>
+        <v>נתנאל ששון - היא יודעת קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410321&amp;sid=43fe725fde6d02927362e89be5d6c20b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410325&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-02</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,12 +507,88 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ליאור כהן - חוזה לך ברח קאבר</v>
+        <v>נתנאל ששון - היא יודעת קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נהוראי אברהם - מישל קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410324&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נהוראי אברהם - מישל קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>נאור כהן - להינשא הלילה &amp; תפילות קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410323&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>נאור כהן - להינשא הלילה &amp; תפילות קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ספיר יהודה לוי - מי המציא את המילה קאבר</v>
+        <v>שילה שטראל - תקופה שלמה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410326&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410340&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ספיר יהודה לוי - מי המציא את המילה קאבר</v>
+        <v>שילה שטראל - תקופה שלמה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתנאל ששון - היא יודעת קאבר</v>
+        <v>רון סויסה - האור בחשכה</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410325&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410339&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתנאל ששון - היא יודעת קאבר</v>
+        <v>רון סויסה - האור בחשכה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נהוראי אברהם - מישל קאבר</v>
+        <v>ישראל בניטה - מי אני</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410324&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410338&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נהוראי אברהם - מישל קאבר</v>
+        <v>ישראל בניטה - מי אני</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נאור כהן - להינשא הלילה &amp; תפילות קאבר</v>
+        <v>יהונתן לוי - הסתכלת לי בעיניים</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410323&amp;sid=6b30857c35a09382fab931eb4f860fc2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410337&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-03</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,12 +583,392 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נאור כהן - להינשא הלילה &amp; תפילות קאבר</v>
+        <v>יהונתן לוי - הסתכלת לי בעיניים</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>יהונתן חוטה - מחרוזת אבות ובנים 2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410336&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>יהונתן חוטה - מחרוזת אבות ובנים 2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>טלי רבקה סימן טוב - חיים חדשים</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410335&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>טלי רבקה סימן טוב - חיים חדשים</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>חי ברוך &amp; הרב ראובן אלבז - אור של תשובה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410334&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>חי ברוך &amp; הרב ראובן אלבז - אור של תשובה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>גל סינואני - יום יפה</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410333&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>גל סינואני - יום יפה</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>גל אדם - כבר לא שלך</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410332&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>גל אדם - כבר לא שלך</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>בנאל בן ציון - מאשאפ עוד נשימה &amp; היא יודעת</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410331&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>בנאל בן ציון - מאשאפ עוד נשימה &amp; היא יודעת</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>בועז טביב - מחרוזת ואסיליס קאראס 2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410330&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>בועז טביב - מחרוזת ואסיליס קאראס 2026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אליאור נונה - מחרוזת צינגלה 2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410329&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אליאור נונה - מחרוזת צינגלה 2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אליאב זעפרני - מחרוזת זבקיקו 2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410328&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אליאב זעפרני - מחרוזת זבקיקו 2026</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אביב לוי - דרום אמריקה</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410327&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אביב לוי - דרום אמריקה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שילה שטראל - תקופה שלמה</v>
+        <v>שושנה קנו - סיגריות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410340&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410351&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-03</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שילה שטראל - תקופה שלמה</v>
+        <v>שושנה קנו - סיגריות</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רון סויסה - האור בחשכה</v>
+        <v>רפאל אלוש - שערי שמיים פתח</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410339&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410350&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-03</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רון סויסה - האור בחשכה</v>
+        <v>רפאל אלוש - שערי שמיים פתח</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ישראל בניטה - מי אני</v>
+        <v>יואש - להינשא הלילה</v>
       </c>
       <c r="B4" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410338&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410349&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-03</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ישראל בניטה - מי אני</v>
+        <v>יואש - להינשא הלילה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יהונתן לוי - הסתכלת לי בעיניים</v>
+        <v>אם סי פיטוסי &amp; לוקץ׳ - אסור ליפול</v>
       </c>
       <c r="B5" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410337&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410348&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-03</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יהונתן לוי - הסתכלת לי בעיניים</v>
+        <v>אם סי פיטוסי &amp; לוקץ׳ - אסור ליפול</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יהונתן חוטה - מחרוזת אבות ובנים 2026</v>
+        <v>אוראל &amp; ויק - צ׳לה בלה</v>
       </c>
       <c r="B6" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410336&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410347&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-03</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יהונתן חוטה - מחרוזת אבות ובנים 2026</v>
+        <v>אוראל &amp; ויק - צ׳לה בלה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>טלי רבקה סימן טוב - חיים חדשים</v>
+        <v>שי פורטוגלי - עד מתי</v>
       </c>
       <c r="B7" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410335&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410346&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-03</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>טלי רבקה סימן טוב - חיים חדשים</v>
+        <v>שי פורטוגלי - עד מתי</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>חי ברוך &amp; הרב ראובן אלבז - אור של תשובה</v>
+        <v>פרחי ירושלים - ביבי מיקונה</v>
       </c>
       <c r="B8" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410334&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410345&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-03</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>חי ברוך &amp; הרב ראובן אלבז - אור של תשובה</v>
+        <v>פרחי ירושלים - ביבי מיקונה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>גל סינואני - יום יפה</v>
+        <v>נעם בוסקילה - והיא שעמדה</v>
       </c>
       <c r="B9" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410333&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410344&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-03</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>גל סינואני - יום יפה</v>
+        <v>נעם בוסקילה - והיא שעמדה</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>גל אדם - כבר לא שלך</v>
+        <v>מיכאל כורש - בצאת ישראל ממצרים</v>
       </c>
       <c r="B10" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410332&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410343&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-03</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>גל אדם - כבר לא שלך</v>
+        <v>מיכאל כורש - בצאת ישראל ממצרים</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>בנאל בן ציון - מאשאפ עוד נשימה &amp; היא יודעת</v>
+        <v>דולב הרץ - אהבה</v>
       </c>
       <c r="B11" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410331&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410342&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-03</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>בנאל בן ציון - מאשאפ עוד נשימה &amp; היא יודעת</v>
+        <v>דולב הרץ - אהבה</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>בועז טביב - מחרוזת ואסיליס קאראס 2026</v>
+        <v>בנימין דנישמן - מחרוזת כורדית 2026</v>
       </c>
       <c r="B12" t="str">
         <v>2026-04-03</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410330&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410341&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-03</v>
@@ -849,126 +849,12 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>בועז טביב - מחרוזת ואסיליס קאראס 2026</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אליאור נונה - מחרוזת צינגלה 2026</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410329&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אליאור נונה - מחרוזת צינגלה 2026</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>אליאב זעפרני - מחרוזת זבקיקו 2026</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410328&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>אליאב זעפרני - מחרוזת זבקיקו 2026</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>אביב לוי - דרום אמריקה</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410327&amp;sid=93cc9c565d52147d216ec01fa72e4baa</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>אביב לוי - דרום אמריקה</v>
+        <v>בנימין דנישמן - מחרוזת כורדית 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שושנה קנו - סיגריות</v>
+        <v>שירז אברהם - שונא אותך</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410351&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410360&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שושנה קנו - סיגריות</v>
+        <v>שירז אברהם - שונא אותך</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רפאל אלוש - שערי שמיים פתח</v>
+        <v>שגיא גטר - מקולל</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-04</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410350&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410359&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-04</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רפאל אלוש - שערי שמיים פתח</v>
+        <v>שגיא גטר - מקולל</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יואש - להינשא הלילה</v>
+        <v>עמירן דביר מארח את אהרל׳ה סמט וגדעון לוי - למענך עשה</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-04</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410349&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410358&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-04</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יואש - להינשא הלילה</v>
+        <v>עמירן דביר מארח את אהרל׳ה סמט וגדעון לוי - למענך עשה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אם סי פיטוסי &amp; לוקץ׳ - אסור ליפול</v>
+        <v>ישראל דיין - מחרוזת שקטים 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-04</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410348&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410355&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-04</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אם סי פיטוסי &amp; לוקץ׳ - אסור ליפול</v>
+        <v>ישראל דיין - מחרוזת שקטים 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אוראל &amp; ויק - צ׳לה בלה</v>
+        <v>חנן בן ארי &amp; פאר טסי - הלוואי</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-04</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410347&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410354&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-04</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,240 +621,12 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אוראל &amp; ויק - צ׳לה בלה</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>שי פורטוגלי - עד מתי</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410346&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>שי פורטוגלי - עד מתי</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>פרחי ירושלים - ביבי מיקונה</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410345&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>פרחי ירושלים - ביבי מיקונה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>נעם בוסקילה - והיא שעמדה</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410344&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>נעם בוסקילה - והיא שעמדה</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>מיכאל כורש - בצאת ישראל ממצרים</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410343&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>מיכאל כורש - בצאת ישראל ממצרים</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>דולב הרץ - אהבה</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410342&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>דולב הרץ - אהבה</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>בנימין דנישמן - מחרוזת כורדית 2026</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410341&amp;sid=3e18404d100e616166aad5bb56bb617f</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>בנימין דנישמן - מחרוזת כורדית 2026</v>
+        <v>חנן בן ארי &amp; פאר טסי - הלוואי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שירז אברהם - שונא אותך</v>
+        <v>אלעד אביבי - יהודי זה נשמה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410360&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410375&amp;sid=77f23f31065bb4ab90b9297067773482</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שירז אברהם - שונא אותך</v>
+        <v>אלעד אביבי - יהודי זה נשמה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שגיא גטר - מקולל</v>
+        <v>אבימאיר - תגידי לנו כן</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410359&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410374&amp;sid=77f23f31065bb4ab90b9297067773482</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שגיא גטר - מקולל</v>
+        <v>אבימאיר - תגידי לנו כן</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עמירן דביר מארח את אהרל׳ה סמט וגדעון לוי - למענך עשה</v>
+        <v>סאלי - שתי נשמות</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410358&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410373&amp;sid=77f23f31065bb4ab90b9297067773482</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עמירן דביר מארח את אהרל׳ה סמט וגדעון לוי - למענך עשה</v>
+        <v>סאלי - שתי נשמות</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ישראל דיין - מחרוזת שקטים 2026</v>
+        <v>ניר בנילוש - מכור לדיכאון</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410355&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410372&amp;sid=77f23f31065bb4ab90b9297067773482</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ישראל דיין - מחרוזת שקטים 2026</v>
+        <v>ניר בנילוש - מכור לדיכאון</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>חנן בן ארי &amp; פאר טסי - הלוואי</v>
+        <v>התקווה 6 - חופשת מלחמה</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410354&amp;sid=cc30946d1b11e3c89cd1b1bb4e38313b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410371&amp;sid=77f23f31065bb4ab90b9297067773482</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,12 +621,126 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>חנן בן ארי &amp; פאר טסי - הלוואי</v>
+        <v>התקווה 6 - חופשת מלחמה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>הלהקות הצבאיות - שיר הלהקה 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410370&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>הלהקות הצבאיות - שיר הלהקה 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>דן ביטון - לא משנה מה תגיד</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410369&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>דן ביטון - לא משנה מה תגיד</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>בן לוי &amp; לי שי - אותו דבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410368&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>בן לוי &amp; לי שי - אותו דבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אלעד אביבי - יהודי זה נשמה</v>
+        <v>שלווה - ילדה טובה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410375&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410385&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אלעד אביבי - יהודי זה נשמה</v>
+        <v>שלווה - ילדה טובה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אבימאיר - תגידי לנו כן</v>
+        <v>צוף מימון &amp; יקיר - נוף אחר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410374&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410384&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אבימאיר - תגידי לנו כן</v>
+        <v>צוף מימון &amp; יקיר - נוף אחר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>סאלי - שתי נשמות</v>
+        <v>יגל יובל שרעבי - מיליונר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410373&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410383&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>סאלי - שתי נשמות</v>
+        <v>יגל יובל שרעבי - מיליונר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ניר בנילוש - מכור לדיכאון</v>
+        <v>דבורה מונצרש - לגדול מתוך הנס (שירת נשים)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410372&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410381&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ניר בנילוש - מכור לדיכאון</v>
+        <v>דבורה מונצרש - לגדול מתוך הנס (שירת נשים)</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>התקווה 6 - חופשת מלחמה</v>
+        <v>בבויה - אף אחד</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410371&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410380&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>התקווה 6 - חופשת מלחמה</v>
+        <v>בבויה - אף אחד</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>הלהקות הצבאיות - שיר הלהקה 2026</v>
+        <v>באני - טבעת</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410370&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410379&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>הלהקות הצבאיות - שיר הלהקה 2026</v>
+        <v>באני - טבעת</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>דן ביטון - לא משנה מה תגיד</v>
+        <v>אדיר ניזרי - מחרוזת בית״ר זה עד המוות 2026</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410369&amp;sid=77f23f31065bb4ab90b9297067773482</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410378&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,50 +697,12 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>דן ביטון - לא משנה מה תגיד</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>בן לוי &amp; לי שי - אותו דבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410368&amp;sid=77f23f31065bb4ab90b9297067773482</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>בן לוי &amp; לי שי - אותו דבר</v>
+        <v>אדיר ניזרי - מחרוזת בית״ר זה עד המוות 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלווה - ילדה טובה</v>
+        <v>אריה פרננד - פעם היו זמנים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410385&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410390&amp;sid=66e62fcdd2c9ce707ca8edc22bf3960b</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלווה - ילדה טובה</v>
+        <v>אריה פרננד - פעם היו זמנים</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>צוף מימון &amp; יקיר - נוף אחר</v>
+        <v>עודד מנשרי - עד שיאיר הבוקר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-06</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410384&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410389&amp;sid=66e62fcdd2c9ce707ca8edc22bf3960b</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>צוף מימון &amp; יקיר - נוף אחר</v>
+        <v>עודד מנשרי - עד שיאיר הבוקר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יגל יובל שרעבי - מיליונר</v>
+        <v>דוד וייה - הכל היה זמני</v>
       </c>
       <c r="B4" t="str">
         <v>2026-04-06</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410383&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410388&amp;sid=66e62fcdd2c9ce707ca8edc22bf3960b</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,164 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יגל יובל שרעבי - מיליונר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>דבורה מונצרש - לגדול מתוך הנס (שירת נשים)</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410381&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>דבורה מונצרש - לגדול מתוך הנס (שירת נשים)</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>בבויה - אף אחד</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410380&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>בבויה - אף אחד</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>באני - טבעת</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410379&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>באני - טבעת</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אדיר ניזרי - מחרוזת בית״ר זה עד המוות 2026</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410378&amp;sid=563f0dd190cfae43c1a34d1a696bd38a</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-06</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אדיר ניזרי - מחרוזת בית״ר זה עד המוות 2026</v>
+        <v>דוד וייה - הכל היה זמני</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>